--- a/files/Spinney_Gantt_v4.xlsx
+++ b/files/Spinney_Gantt_v4.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="280">
   <si>
     <t xml:space="preserve">Spinney External Works — Project Gantt (v4 — 3 Sep restructure: gate renumbering, render soft wash added, decking board-laying split from substructure)</t>
   </si>
@@ -126,7 +126,7 @@
     <t xml:space="preserve">Back-of-house gutters — realign, lead flashing, hedgehog brushes. DELAYED 19 Aug: decking substructure prioritised instead. Not yet started — new date TBC. Gates new decking BOARD installation, either side, and coping's remaining invoice (already paid 13 Aug).</t>
   </si>
   <si>
-    <t xml:space="preserve">Delayed — decking substructure prioritised (ESTIMATED restart w/c 7 Sep)</t>
+    <t xml:space="preserve">Delayed — decking substructure prioritised (ESTIMATED restart w/c 15 Sep, confirmed not started as of 11 Sep)</t>
   </si>
   <si>
     <t xml:space="preserve">1.6</t>
@@ -138,7 +138,7 @@
     <t xml:space="preserve">TBC</t>
   </si>
   <si>
-    <t xml:space="preserve">Not started (ESTIMATED w/c 7 Sep)</t>
+    <t xml:space="preserve">Not started (ESTIMATED w/c 15 Sep, confirmed not started as of 11 Sep)</t>
   </si>
   <si>
     <t xml:space="preserve">G2</t>
@@ -246,12 +246,18 @@
     <t xml:space="preserve">2.6</t>
   </si>
   <si>
-    <t xml:space="preserve">New shed area, perpendicular to side (a) — TRIMMED 8 Sep to excavation + substructure only, for BOTH the shed base and the new decking area leading up to it. Millboard board-laying for that decking area is now tracked at 2.5 (gated on G2/G3). Shed relocation onto its own base is NOT dependent on board-laying — only on its own substructure — so it can happen as soon as substructure completes (~22 Sep), independent of G2/G3/2.5. RELATED to 3.3 (fence): boundary issue and scope increase, confirmed 8 Sep.</t>
+    <t xml:space="preserve">New shed area, perpendicular to side (a) — TRIMMED 8 Sep to excavation + substructure only, for BOTH the shed base and the new decking area leading up to it. Millboard board-laying for that decking area is now tracked at 2.5 (gated on G2/G3). Shed relocation onto its own base is NOT dependent on board-laying — only on its own substructure — so it can happen as soon as substructure completes (~22 Sep), independent of G2/G3/2.5. CORRECTED 11 Sep: the related boundary/fence work is 2.7 (side a, chimney side — now complete), NOT 3.3 (side b) as first logged 8 Sep.</t>
   </si>
   <si>
     <t xml:space="preserve">In progress — excavation phase, concurrent with 2.2/2.3</t>
   </si>
   <si>
+    <t xml:space="preserve">2.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fence move — chimney side (side a), boundary reclaimed from neighbour to enable the wider decking area, repositioned at new extended height. COMPLETE 11 Sep. NOT the same as 3.3 (side b, concrete spurs, still pending) or 3.5 (TPO/tree-dependent relocation). CORRECTED 11 Sep: this is the fence the 8 Sep boundary/scope-increase note was actually describing, not 3.3.</t>
+  </si>
+  <si>
     <t xml:space="preserve">G5</t>
   </si>
   <si>
@@ -276,7 +282,7 @@
     <t xml:space="preserve">Front-of-house gutters, minor roof repairs and tile repairs — repair / realignment (ladder work). Tile repairs confirmed via WhatsApp (10 Aug), same no-separate-charge basis.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fence spurring, side (b) — should complete before decking board-laying (2.5) starts; not blocking substructure work (2.3), which is already under way (propped temporarily). UPDATE 8 Sep: repair/replacement, repositioned at new extended height — targeted by end of next week (w/c 14 Sep). RELATED to 2.6 (shed): boundary issue and scope increase confirmed 8 Sep — the two are connected, not independent.</t>
+    <t xml:space="preserve">Fence spurring, side (b) — concrete spurs, should complete before decking board-laying (2.5) starts; not blocking substructure work (2.3), which is already under way (propped temporarily). CORRECTED 11 Sep: unrelated to the shed/boundary issue — that's 2.7 (side a, chimney side, now complete), a separate fence. The 'new extended height' detail logged 8 Sep belonged to 2.7, not here. 3.3 itself still not done; propped temporarily, deferred to wet weather for the actual fix — no height change involved.</t>
   </si>
   <si>
     <t xml:space="preserve">→ before 2.5</t>
@@ -573,7 +579,7 @@
     <t xml:space="preserve">Side (a)</t>
   </si>
   <si>
-    <t xml:space="preserve">RELATED to 3.3 (fence) — boundary issue and scope increase, confirmed 8 Sep. Shed relocation onto its own base is NOT gated by board-laying — only by this task's own substructure completing (~22 Sep).</t>
+    <t xml:space="preserve">CORRECTED 11 Sep: the related fence work is 2.7 (side a, chimney side, now complete), NOT 3.3 (side b) as first logged 8 Sep. Shed relocation onto its own base is NOT gated by board-laying — only by this task's own substructure completing (~22 Sep).</t>
   </si>
   <si>
     <t xml:space="preserve">Driveway channel</t>
@@ -618,7 +624,7 @@
     <t xml:space="preserve">Garden</t>
   </si>
   <si>
-    <t xml:space="preserve">HARD CONSTRAINT (as designed): side (b) spurring should complete before decking board-laying (2.5) begins. STATUS 8 Sep: repair/replacement now confirmed, repositioned at new extended height, targeted by end of w/c 14 Sep. RELATED to 2.6 (shed) — boundary issue and scope increase, confirmed 8 Sep, the two are connected.</t>
+    <t xml:space="preserve">HARD CONSTRAINT (as designed): side (b) spurring should complete before decking board-laying (2.5) begins. STATUS 8 Sep: not yet done, propped temporarily, deferred to wet weather. CORRECTED 11 Sep: unrelated to the shed/boundary issue — that's 2.7, a separate fence. The 'extended height' note logged 8 Sep belonged there, not here.</t>
   </si>
   <si>
     <t xml:space="preserve">Tree / bush clearing back to fence boundary — EXTERNAL company</t>
@@ -643,6 +649,18 @@
   </si>
   <si>
     <t xml:space="preserve">NEW scope, own £2,140 budget. Estimate sent 4 Sep, discussed 4 Sep, start confirmed 8 Sep — end of this week or next. Distinct from earlier 'gutters included in Luke's price' understanding for 1.5/3.2 — confirm with Luke whether this supersedes or adds to that.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fence move, chimney side</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boundary reclaimed from neighbour, side a, to enable the wider decking area; repositioned at new extended height</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chimney side / side a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMPLETE 11 Sep. This is the fence the 8 Sep boundary/scope-increase note referred to — not 3.3 (side b spurs) or 3.5 (TPO-dependent).</t>
   </si>
   <si>
     <t xml:space="preserve">Reference — contacts, rules, assumptions, sign-off log</t>
@@ -1476,7 +1494,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AC43"/>
+  <dimension ref="A1:AC44"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11"/>
@@ -1932,10 +1950,10 @@
         <v>34</v>
       </c>
       <c r="G13" s="18" t="n">
-        <v>46272</v>
+        <v>46280</v>
       </c>
       <c r="H13" s="18" t="n">
-        <v>46272</v>
+        <v>46280</v>
       </c>
       <c r="I13" s="14"/>
       <c r="J13" s="14"/>
@@ -1979,10 +1997,10 @@
         <v>38</v>
       </c>
       <c r="G14" s="19" t="n">
-        <v>46273</v>
+        <v>46281</v>
       </c>
       <c r="H14" s="19" t="n">
-        <v>46274</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2003,10 +2021,10 @@
         <v>42</v>
       </c>
       <c r="G15" s="22" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="H15" s="22" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="I15" s="9"/>
       <c r="J15" s="9"/>
@@ -2316,10 +2334,10 @@
         <v>38</v>
       </c>
       <c r="G22" s="18" t="n">
-        <v>46272</v>
+        <v>46280</v>
       </c>
       <c r="H22" s="18" t="n">
-        <v>46273</v>
+        <v>46281</v>
       </c>
       <c r="I22" s="14"/>
       <c r="J22" s="14"/>
@@ -2361,10 +2379,10 @@
         <v>42</v>
       </c>
       <c r="G23" s="18" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="H23" s="18" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="I23" s="14"/>
       <c r="J23" s="14"/>
@@ -2491,97 +2509,80 @@
         <v>77</v>
       </c>
       <c r="C27" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="G27" s="19" t="n">
+        <v>46276</v>
+      </c>
+      <c r="H27" s="19" t="n">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="D27" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16" t="s">
+      <c r="B28" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="G27" s="19" t="n">
+      <c r="G28" s="19" t="n">
         <v>46323</v>
       </c>
-      <c r="H27" s="19" t="n">
+      <c r="H28" s="19" t="n">
         <v>46323</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
-      <c r="K28" s="10"/>
-      <c r="L28" s="9"/>
-      <c r="M28" s="9"/>
-      <c r="N28" s="9"/>
-      <c r="O28" s="10"/>
-      <c r="P28" s="9"/>
-      <c r="Q28" s="9"/>
-      <c r="R28" s="9"/>
-      <c r="S28" s="9"/>
-      <c r="T28" s="9"/>
-      <c r="U28" s="9"/>
-      <c r="V28" s="9"/>
-      <c r="W28" s="9"/>
-      <c r="X28" s="9"/>
-      <c r="Y28" s="9"/>
-      <c r="Z28" s="9"/>
-      <c r="AA28" s="9"/>
-      <c r="AB28" s="9"/>
-      <c r="AC28" s="9"/>
-    </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="B29" s="12" t="s">
+      <c r="A29" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="C29" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D29" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="E29" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="F29" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29"/>
-      <c r="I29" s="30"/>
-      <c r="J29" s="30"/>
-      <c r="K29" s="15"/>
-      <c r="L29" s="30"/>
-      <c r="M29" s="30"/>
-      <c r="N29" s="30"/>
-      <c r="O29" s="15"/>
-      <c r="P29" s="30"/>
-      <c r="Q29" s="30"/>
-      <c r="R29" s="30"/>
-      <c r="S29" s="30"/>
-      <c r="T29" s="30"/>
-      <c r="U29" s="30"/>
-      <c r="V29" s="30"/>
-      <c r="W29" s="30"/>
-      <c r="X29" s="30"/>
-      <c r="Y29" s="30"/>
-      <c r="Z29" s="30"/>
-      <c r="AA29" s="30"/>
-      <c r="AB29" s="30"/>
-      <c r="AC29" s="30"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="9"/>
+      <c r="M29" s="9"/>
+      <c r="N29" s="9"/>
+      <c r="O29" s="10"/>
+      <c r="P29" s="9"/>
+      <c r="Q29" s="9"/>
+      <c r="R29" s="9"/>
+      <c r="S29" s="9"/>
+      <c r="T29" s="9"/>
+      <c r="U29" s="9"/>
+      <c r="V29" s="9"/>
+      <c r="W29" s="9"/>
+      <c r="X29" s="9"/>
+      <c r="Y29" s="9"/>
+      <c r="Z29" s="9"/>
+      <c r="AA29" s="9"/>
+      <c r="AB29" s="9"/>
+      <c r="AC29" s="9"/>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
@@ -2597,7 +2598,7 @@
         <v>16</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F30" s="11" t="s">
         <v>54</v>
@@ -2628,22 +2629,22 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C31" s="11" t="s">
         <v>15</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>85</v>
+        <v>16</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="G31" s="29"/>
       <c r="H31" s="29"/>
@@ -2671,22 +2672,22 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="B32" s="12" t="s">
+      <c r="E32" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" s="11" t="s">
         <v>88</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="D32" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="E32" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="F32" s="11" t="s">
-        <v>90</v>
       </c>
       <c r="G32" s="29"/>
       <c r="H32" s="29"/>
@@ -2714,22 +2715,22 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C33" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="B33" s="12" t="s">
+      <c r="D33" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F33" s="11" t="s">
         <v>92</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="E33" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="F33" s="11" t="s">
-        <v>54</v>
       </c>
       <c r="G33" s="29"/>
       <c r="H33" s="29"/>
@@ -2756,31 +2757,33 @@
       <c r="AC33" s="30"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="31" t="s">
+      <c r="A34" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B34" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="B34" s="32" t="s">
+      <c r="C34" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="C34" s="31" t="s">
-        <v>96</v>
-      </c>
-      <c r="D34" s="31" t="s">
-        <v>53</v>
-      </c>
-      <c r="E34" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F34" s="31" t="s">
+      <c r="E34" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F34" s="11" t="s">
         <v>54</v>
       </c>
+      <c r="G34" s="29"/>
+      <c r="H34" s="29"/>
       <c r="I34" s="30"/>
       <c r="J34" s="30"/>
-      <c r="K34" s="30"/>
+      <c r="K34" s="15"/>
       <c r="L34" s="30"/>
       <c r="M34" s="30"/>
       <c r="N34" s="30"/>
-      <c r="O34" s="30"/>
+      <c r="O34" s="15"/>
       <c r="P34" s="30"/>
       <c r="Q34" s="30"/>
       <c r="R34" s="30"/>
@@ -2797,33 +2800,31 @@
       <c r="AC34" s="30"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="11" t="s">
+      <c r="A35" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="B35" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="B35" s="33" t="s">
+      <c r="C35" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="C35" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D35" s="11" t="s">
+      <c r="D35" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="E35" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11" t="s">
+      <c r="F35" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="G35" s="34" t="s">
-        <v>37</v>
-      </c>
-      <c r="H35" s="29"/>
       <c r="I35" s="30"/>
       <c r="J35" s="30"/>
-      <c r="K35" s="15"/>
+      <c r="K35" s="30"/>
       <c r="L35" s="30"/>
       <c r="M35" s="30"/>
       <c r="N35" s="30"/>
-      <c r="O35" s="15"/>
+      <c r="O35" s="30"/>
       <c r="P35" s="30"/>
       <c r="Q35" s="30"/>
       <c r="R35" s="30"/>
@@ -2840,31 +2841,54 @@
       <c r="AC35" s="30"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="16" t="s">
+      <c r="A36" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="B36" s="17" t="s">
+      <c r="B36" s="33" t="s">
         <v>100</v>
       </c>
-      <c r="C36" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D36" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="E36" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="F36" s="16" t="s">
-        <v>17</v>
-      </c>
+      <c r="C36" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G36" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="H36" s="29"/>
+      <c r="I36" s="30"/>
+      <c r="J36" s="30"/>
+      <c r="K36" s="15"/>
+      <c r="L36" s="30"/>
+      <c r="M36" s="30"/>
+      <c r="N36" s="30"/>
+      <c r="O36" s="15"/>
+      <c r="P36" s="30"/>
+      <c r="Q36" s="30"/>
+      <c r="R36" s="30"/>
+      <c r="S36" s="30"/>
+      <c r="T36" s="30"/>
+      <c r="U36" s="30"/>
+      <c r="V36" s="30"/>
+      <c r="W36" s="30"/>
+      <c r="X36" s="30"/>
+      <c r="Y36" s="30"/>
+      <c r="Z36" s="30"/>
+      <c r="AA36" s="30"/>
+      <c r="AB36" s="30"/>
+      <c r="AC36" s="30"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="B37" s="17" t="s">
         <v>102</v>
-      </c>
-      <c r="B37" s="17" t="s">
-        <v>103</v>
       </c>
       <c r="C37" s="16" t="s">
         <v>52</v>
@@ -2873,55 +2897,67 @@
         <v>53</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F37" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="G37" s="16"/>
-      <c r="H37" s="16"/>
+        <v>17</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="B38" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="B38" s="17" t="s">
+      <c r="C38" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="E38" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="F38" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="C38" s="16" t="s">
+      <c r="G38" s="16"/>
+      <c r="H38" s="16"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="B39" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="C39" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="D38" s="16" t="s">
+      <c r="D39" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E38" s="16" t="s">
+      <c r="E39" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="F38" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="G38" s="19" t="n">
-        <v>46277</v>
-      </c>
-      <c r="H38" s="19" t="n">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="5" t="s">
-        <v>108</v>
+      <c r="F39" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="G39" s="19" t="n">
+        <v>46280</v>
+      </c>
+      <c r="H39" s="19" t="n">
+        <v>46286</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="B41" s="1" t="s">
         <v>111</v>
       </c>
     </row>
@@ -2929,10 +2965,18 @@
       <c r="A42" s="5" t="s">
         <v>112</v>
       </c>
+      <c r="B42" s="1" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="5" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -3036,9 +3080,9 @@
       <formula>AND(ISNUMBER($G27),ISNUMBER($H27),$G27&lt;=I$5+6,$H27&gt;=I$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I29:AC29">
+  <conditionalFormatting sqref="I28:AC28">
     <cfRule type="expression" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>AND(ISNUMBER($G29),ISNUMBER($H29),$G29&lt;=I$5+6,$H29&gt;=I$5)</formula>
+      <formula>AND(ISNUMBER($G28),ISNUMBER($H28),$G28&lt;=I$5+6,$H28&gt;=I$5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I30:AC30">
@@ -3076,9 +3120,19 @@
       <formula>AND(ISNUMBER($G36),ISNUMBER($H36),$G36&lt;=I$5+6,$H36&gt;=I$5)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="I37:AC37">
+    <cfRule type="expression" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>AND(ISNUMBER($G37),ISNUMBER($H37),$G37&lt;=I$5+6,$H37&gt;=I$5)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="I38:AC38">
-    <cfRule type="expression" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER($G38),ISNUMBER($H38),$G38&lt;=I$5+6,$H38&gt;=I$5)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I39:AC39">
+    <cfRule type="expression" priority="32" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>AND(ISNUMBER($G39),ISNUMBER($H39),$G39&lt;=I$5+6,$H39&gt;=I$5)</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3096,7 +3150,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
@@ -3111,12 +3165,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="35" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3124,28 +3178,28 @@
         <v>4</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>5</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3153,28 +3207,28 @@
         <v>13</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H5" s="11" t="n">
         <v>2</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3182,28 +3236,28 @@
         <v>18</v>
       </c>
       <c r="B6" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="G6" s="11" t="s">
         <v>129</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>127</v>
       </c>
       <c r="H6" s="11" t="n">
         <v>2</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3211,28 +3265,28 @@
         <v>21</v>
       </c>
       <c r="B7" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="F7" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="C7" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>132</v>
-      </c>
       <c r="G7" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H7" s="11" t="n">
         <v>7</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3240,28 +3294,28 @@
         <v>23</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H8" s="11" t="n">
         <v>10</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3269,28 +3323,28 @@
         <v>25</v>
       </c>
       <c r="B9" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="F9" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="C9" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>127</v>
-      </c>
       <c r="G9" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H9" s="11" t="n">
         <v>1</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3298,28 +3352,28 @@
         <v>32</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H10" s="11" t="n">
         <v>3</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3327,28 +3381,28 @@
         <v>35</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H11" s="16" t="s">
         <v>37</v>
       </c>
       <c r="I11" s="17" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3356,28 +3410,28 @@
         <v>44</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H12" s="11" t="n">
         <v>5</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3385,28 +3439,28 @@
         <v>55</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H13" s="16" t="n">
         <v>13</v>
       </c>
       <c r="I13" s="17" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3414,28 +3468,28 @@
         <v>58</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H14" s="16" t="n">
         <v>13</v>
       </c>
       <c r="I14" s="17" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3443,28 +3497,28 @@
         <v>61</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H15" s="16" t="s">
         <v>37</v>
       </c>
       <c r="I15" s="17" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3472,28 +3526,28 @@
         <v>66</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H16" s="16" t="n">
         <v>13</v>
       </c>
       <c r="I16" s="17" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3501,86 +3555,86 @@
         <v>73</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H17" s="11" t="n">
         <v>3</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H18" s="11" t="n">
         <v>4</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H19" s="11" t="n">
         <v>2</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3588,115 +3642,144 @@
         <v>60</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H20" s="11" t="n">
         <v>3</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C21" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="E21" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="D21" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>197</v>
-      </c>
       <c r="F21" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H21" s="11" t="n">
         <v>2</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H22" s="11" t="n">
         <v>4</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="16" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H23" s="16" t="s">
         <v>37</v>
       </c>
       <c r="I23" s="17" t="s">
-        <v>206</v>
+        <v>208</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="H24" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="17" t="s">
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -3728,80 +3811,80 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="36" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="C5" s="36" t="s">
         <v>16</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="E5" s="36" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>29</v>
       </c>
       <c r="D6" s="37" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="E6" s="38" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>29</v>
       </c>
       <c r="D7" s="37" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="E7" s="38" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3809,68 +3892,68 @@
         <v>49</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>29</v>
       </c>
       <c r="D8" s="37" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="E8" s="38" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="D9" s="37" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="E9" s="37"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="D10" s="37"/>
       <c r="E10" s="37"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="D11" s="37"/>
       <c r="E11" s="37"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="D12" s="37"/>
       <c r="E12" s="37"/>
@@ -3880,10 +3963,10 @@
         <v>20</v>
       </c>
       <c r="B13" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="C13" s="12" t="s">
         <v>237</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>231</v>
       </c>
       <c r="D13" s="37"/>
       <c r="E13" s="37"/>
@@ -3893,122 +3976,122 @@
         <v>52</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>52</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="E14" s="37"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="39" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="39" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="39" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="39" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="39" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="39" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="39" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="39" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="39" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="39" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="39" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="39" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="39" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="39" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="F37" s="6" t="s">
         <v>49</v>
@@ -4019,7 +4102,7 @@
         <v>27</v>
       </c>
       <c r="B38" s="17" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="C38" s="40" t="n">
         <v>46252</v>
@@ -4033,7 +4116,7 @@
         <v>39</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="C39" s="41"/>
       <c r="D39" s="41"/>
@@ -4045,7 +4128,7 @@
         <v>64</v>
       </c>
       <c r="B40" s="17" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="C40" s="41"/>
       <c r="D40" s="41"/>
@@ -4057,17 +4140,17 @@
         <v>70</v>
       </c>
       <c r="B41" s="17" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C41" s="16"/>
       <c r="D41" s="16"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B42" s="17" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="C42" s="41"/>
       <c r="D42" s="41"/>
@@ -4077,42 +4160,42 @@
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="39" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="39" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="39" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="39" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="39" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
   </sheetData>
